--- a/data/trans_camb/P62-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P62-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,79; -4,19</t>
+          <t>-13,19; -3,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,88; -1,71</t>
+          <t>-11,04; -0,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 4,22</t>
+          <t>-5,37; 4,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,76; 10,97</t>
+          <t>2,02; 10,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,05; 12,84</t>
+          <t>3,79; 12,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,51; 21,56</t>
+          <t>13,22; 21,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 5,09</t>
+          <t>-1,14; 5,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 7,76</t>
+          <t>0,34; 7,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,95; 14,61</t>
+          <t>8,0; 14,52</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,02; -5,5</t>
+          <t>-16,39; -5,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,65; -2,23</t>
+          <t>-13,7; -1,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 5,48</t>
+          <t>-6,68; 5,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,91; 30,7</t>
+          <t>5,08; 28,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,89; 35,0</t>
+          <t>9,37; 34,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,06; 59,81</t>
+          <t>32,43; 58,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 9,94</t>
+          <t>-2,07; 10,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 14,97</t>
+          <t>0,59; 14,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,43; 28,6</t>
+          <t>14,55; 28,3</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 1,57</t>
+          <t>-8,33; 1,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 9,06</t>
+          <t>-0,56; 8,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,61; 19,06</t>
+          <t>8,03; 19,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 8,94</t>
+          <t>3,32; 9,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,28; 14,41</t>
+          <t>8,45; 14,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,82; 52,83</t>
+          <t>16,78; 52,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 6,68</t>
+          <t>1,39; 6,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,73; 12,95</t>
+          <t>7,53; 12,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,83; 38,71</t>
+          <t>16,59; 41,08</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,52; 6,09</t>
+          <t>-24,83; 6,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 33,01</t>
+          <t>-1,74; 32,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,83; 70,87</t>
+          <t>24,72; 70,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35,34; 121,32</t>
+          <t>34,1; 125,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>81,11; 202,09</t>
+          <t>83,02; 193,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>183,61; 709,26</t>
+          <t>184,78; 739,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,21; 44,28</t>
+          <t>8,25; 46,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>42,73; 87,87</t>
+          <t>41,97; 86,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>98,62; 267,63</t>
+          <t>98,43; 261,5</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-24,29; -2,04</t>
+          <t>-24,28; -1,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 5,3</t>
+          <t>-17,32; 5,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,1; 26,62</t>
+          <t>3,28; 25,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,96; 1,9</t>
+          <t>-14,43; 2,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 8,25</t>
+          <t>-7,73; 8,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,84; 20,89</t>
+          <t>3,71; 18,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,94; -1,81</t>
+          <t>-16,86; -3,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 4,53</t>
+          <t>-9,67; 4,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,32; 20,38</t>
+          <t>6,82; 20,23</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-53,02; -7,47</t>
+          <t>-51,58; -2,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-35,97; 15,31</t>
+          <t>-35,92; 15,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,12; 76,36</t>
+          <t>6,46; 72,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,08; 10,79</t>
+          <t>-54,44; 12,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,69; 44,9</t>
+          <t>-28,87; 47,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,21; 117,95</t>
+          <t>11,68; 105,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-47,1; -6,94</t>
+          <t>-48,25; -10,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-28,69; 15,94</t>
+          <t>-27,55; 17,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,23; 75,06</t>
+          <t>19,29; 75,89</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-13,89; -6,91</t>
+          <t>-14,13; -7,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,56; -4,31</t>
+          <t>-11,57; -4,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 3,59</t>
+          <t>-4,91; 3,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,02; 6,88</t>
+          <t>1,7; 6,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,86; 8,16</t>
+          <t>3,1; 8,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,2; 33,41</t>
+          <t>11,99; 35,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 2,18</t>
+          <t>-2,26; 2,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 3,96</t>
+          <t>-0,38; 4,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,34; 20,38</t>
+          <t>7,85; 22,26</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-24,79; -13,15</t>
+          <t>-25,01; -13,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-20,45; -8,35</t>
+          <t>-20,41; -8,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 6,89</t>
+          <t>-8,8; 6,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,49; 29,08</t>
+          <t>6,3; 29,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,14; 35,09</t>
+          <t>11,9; 35,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,63; 138,59</t>
+          <t>47,25; 150,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 6,29</t>
+          <t>-6,08; 6,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 11,59</t>
+          <t>-1,04; 11,78</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>23,07; 58,61</t>
+          <t>21,85; 63,22</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P62-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P62-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>-1,13</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,66</t>
+          <t>17,61</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11,26</t>
+          <t>10,95</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,19; -3,92</t>
+          <t>-13,65; -3,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,04; -0,87</t>
+          <t>-10,55; -1,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 4,2</t>
+          <t>-6,62; 3,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 10,24</t>
+          <t>2,65; 10,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,79; 12,77</t>
+          <t>3,71; 12,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,22; 21,45</t>
+          <t>13,71; 21,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 5,15</t>
+          <t>-1,06; 5,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 7,6</t>
+          <t>0,63; 7,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,0; 14,52</t>
+          <t>7,67; 14,11</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-0,56%</t>
+          <t>-1,44%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,39; -5,23</t>
+          <t>-16,78; -5,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,7; -1,26</t>
+          <t>-13,16; -1,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 5,51</t>
+          <t>-8,22; 4,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,08; 28,05</t>
+          <t>6,53; 28,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,37; 34,32</t>
+          <t>9,39; 34,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,43; 58,61</t>
+          <t>33,54; 59,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 10,13</t>
+          <t>-1,85; 9,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 14,68</t>
+          <t>1,14; 14,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,55; 28,3</t>
+          <t>14,04; 27,32</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13,45</t>
+          <t>14,95</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,39</t>
+          <t>16,92</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>23,92</t>
+          <t>17,72</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 1,63</t>
+          <t>-8,56; 1,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 8,92</t>
+          <t>-0,42; 9,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,03; 19,07</t>
+          <t>9,84; 20,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 9,14</t>
+          <t>3,33; 9,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,45; 14,29</t>
+          <t>8,37; 14,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,78; 52,31</t>
+          <t>14,07; 19,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 6,76</t>
+          <t>1,49; 6,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,53; 12,77</t>
+          <t>7,58; 12,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,59; 41,08</t>
+          <t>14,71; 20,28</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>342,12%</t>
+          <t>196,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>146,62%</t>
+          <t>108,6%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-24,83; 6,13</t>
+          <t>-25,5; 5,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 32,96</t>
+          <t>-1,18; 35,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24,72; 70,54</t>
+          <t>28,31; 73,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34,1; 125,83</t>
+          <t>32,25; 123,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,02; 193,36</t>
+          <t>82,79; 197,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>184,78; 739,67</t>
+          <t>138,07; 280,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,25; 46,31</t>
+          <t>8,61; 45,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>41,97; 86,82</t>
+          <t>42,23; 86,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>98,43; 261,5</t>
+          <t>82,16; 138,08</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14,1</t>
+          <t>14,7</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,87</t>
+          <t>12,27</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13,57</t>
+          <t>13,96</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-24,28; -1,19</t>
+          <t>-26,28; -2,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,32; 5,36</t>
+          <t>-18,32; 4,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,28; 25,33</t>
+          <t>2,25; 24,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 2,11</t>
+          <t>-13,95; 2,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 8,48</t>
+          <t>-9,09; 8,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,71; 18,95</t>
+          <t>3,54; 20,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-16,86; -3,08</t>
+          <t>-17,01; -3,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 4,72</t>
+          <t>-9,21; 4,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,82; 20,23</t>
+          <t>7,38; 20,45</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>45,18%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-51,58; -2,86</t>
+          <t>-54,21; -6,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-35,92; 15,71</t>
+          <t>-36,63; 12,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,46; 72,1</t>
+          <t>4,57; 69,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,44; 12,46</t>
+          <t>-52,64; 14,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-28,87; 47,62</t>
+          <t>-33,96; 48,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,68; 105,98</t>
+          <t>12,02; 116,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-48,25; -10,77</t>
+          <t>-49,36; -10,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,55; 17,35</t>
+          <t>-26,98; 16,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19,29; 75,89</t>
+          <t>20,87; 77,46</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,47</t>
+          <t>0,52</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,67</t>
+          <t>12,17</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>12,06</t>
+          <t>8,85</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,13; -7,04</t>
+          <t>-13,86; -7,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,57; -4,27</t>
+          <t>-11,44; -4,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 3,39</t>
+          <t>-3,48; 4,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,7; 6,77</t>
+          <t>1,78; 6,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,1; 8,19</t>
+          <t>3,01; 8,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,99; 35,16</t>
+          <t>9,54; 14,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 2,19</t>
+          <t>-2,15; 1,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 4,05</t>
+          <t>-0,33; 3,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,85; 22,26</t>
+          <t>6,72; 11,04</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-0,86%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-25,01; -13,48</t>
+          <t>-24,74; -13,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-20,41; -8,2</t>
+          <t>-20,44; -8,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 6,39</t>
+          <t>-6,16; 8,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,3; 29,2</t>
+          <t>6,87; 29,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,9; 35,19</t>
+          <t>11,77; 34,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,25; 150,61</t>
+          <t>37,4; 63,12</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 6,36</t>
+          <t>-5,9; 5,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 11,78</t>
+          <t>-0,93; 11,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>21,85; 63,22</t>
+          <t>18,29; 31,77</t>
         </is>
       </c>
     </row>
